--- a/data/input/pureComponents_2026DecJANNAF_testing_predicted.xlsx
+++ b/data/input/pureComponents_2026DecJANNAF_testing_predicted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937FC521-F94E-4E72-98F0-A0070334BD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795E20AD-5499-4E4A-858A-645F000D6707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{22E7D031-F429-4E0A-8A8B-4D129F5BB641}"/>
+    <workbookView xWindow="-26850" yWindow="1485" windowWidth="21600" windowHeight="14715" activeTab="1" xr2:uid="{22E7D031-F429-4E0A-8A8B-4D129F5BB641}"/>
   </bookViews>
   <sheets>
     <sheet name="Unfinished CATALOG" sheetId="1" r:id="rId1"/>
@@ -885,7 +885,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="112">
   <si>
     <t>Full Name</t>
   </si>
@@ -1206,6 +1206,24 @@
   </si>
   <si>
     <t>[BH4-].CCCC[N+](CCCC)(CCCC)CCCC</t>
+  </si>
+  <si>
+    <t>CC[N+](CC)(CC)CC.[Br-]</t>
+  </si>
+  <si>
+    <t>C[N+](C)(C)C.[Cl-]</t>
+  </si>
+  <si>
+    <t>tetraethylammonium borohydride</t>
+  </si>
+  <si>
+    <t>[BH4-].CC[N+](CC)(CC)CC</t>
+  </si>
+  <si>
+    <t>tetrapropylammonium borohydride</t>
+  </si>
+  <si>
+    <t>[BH4-].CCC[N+](CCC)(CCC)CCC</t>
   </si>
 </sst>
 </file>
@@ -2250,13 +2268,36 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
+      <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>

--- a/data/input/pureComponents_2026DecJANNAF_testing_predicted.xlsx
+++ b/data/input/pureComponents_2026DecJANNAF_testing_predicted.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795E20AD-5499-4E4A-858A-645F000D6707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F519DFB-2EF7-43FB-949C-466482293A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26850" yWindow="1485" windowWidth="21600" windowHeight="14715" activeTab="1" xr2:uid="{22E7D031-F429-4E0A-8A8B-4D129F5BB641}"/>
+    <workbookView xWindow="-26070" yWindow="1485" windowWidth="21600" windowHeight="14715" activeTab="1" xr2:uid="{22E7D031-F429-4E0A-8A8B-4D129F5BB641}"/>
   </bookViews>
   <sheets>
     <sheet name="Unfinished CATALOG" sheetId="1" r:id="rId1"/>
@@ -885,7 +885,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="111">
   <si>
     <t>Full Name</t>
   </si>
@@ -1208,12 +1208,6 @@
     <t>[BH4-].CCCC[N+](CCCC)(CCCC)CCCC</t>
   </si>
   <si>
-    <t>CC[N+](CC)(CC)CC.[Br-]</t>
-  </si>
-  <si>
-    <t>C[N+](C)(C)C.[Cl-]</t>
-  </si>
-  <si>
     <t>tetraethylammonium borohydride</t>
   </si>
   <si>
@@ -1224,6 +1218,9 @@
   </si>
   <si>
     <t>[BH4-].CCC[N+](CCC)(CCC)CCC</t>
+  </si>
+  <si>
+    <t>B.N</t>
   </si>
 </sst>
 </file>
@@ -2189,7 +2186,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE786A1-84C7-4241-A3B9-138356725320}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
@@ -2248,7 +2245,7 @@
         <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2261,43 +2258,36 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" t="s">
-        <v>107</v>
-      </c>
-    </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" t="s">
-        <v>111</v>
-      </c>
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
@@ -2328,15 +2318,6 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
